--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/7.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/7.xlsx
@@ -426,13 +426,13 @@
         <v>-3.371279457546358</v>
       </c>
       <c r="E2">
-        <v>-10.33789804614466</v>
+        <v>-13.40474973152648</v>
       </c>
       <c r="F2">
-        <v>-3.476581098628572</v>
+        <v>-3.770142909037078</v>
       </c>
       <c r="G2">
-        <v>-7.570094891638568</v>
+        <v>-6.37124880763312</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.006004867591125</v>
       </c>
       <c r="E3">
-        <v>-12.53708158759992</v>
+        <v>-13.62526864002958</v>
       </c>
       <c r="F3">
-        <v>-2.733646539549391</v>
+        <v>-3.732069486469607</v>
       </c>
       <c r="G3">
-        <v>-7.996077032847567</v>
+        <v>-6.133506572932571</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.686192492625899</v>
       </c>
       <c r="E4">
-        <v>-11.10586835221871</v>
+        <v>-14.28860293998589</v>
       </c>
       <c r="F4">
-        <v>-3.657872618200856</v>
+        <v>-3.777540229944078</v>
       </c>
       <c r="G4">
-        <v>-7.344672760663482</v>
+        <v>-6.434436658971835</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.318418237948178</v>
       </c>
       <c r="E5">
-        <v>-12.6933461636966</v>
+        <v>-15.27550978104827</v>
       </c>
       <c r="F5">
-        <v>-2.614392283140166</v>
+        <v>-3.659004168073079</v>
       </c>
       <c r="G5">
-        <v>-6.96066094950122</v>
+        <v>-6.064128646168326</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.902834249128257</v>
       </c>
       <c r="E6">
-        <v>-15.64348430442808</v>
+        <v>-15.08310811321427</v>
       </c>
       <c r="F6">
-        <v>-3.020913586064023</v>
+        <v>-3.428235920266388</v>
       </c>
       <c r="G6">
-        <v>-7.497586682109578</v>
+        <v>-6.198848288558954</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.408068026269072</v>
       </c>
       <c r="E7">
-        <v>-13.93193761104359</v>
+        <v>-15.44821692077994</v>
       </c>
       <c r="F7">
-        <v>-2.927248427094677</v>
+        <v>-3.100386326321205</v>
       </c>
       <c r="G7">
-        <v>-7.641078426326347</v>
+        <v>-6.478887196380129</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.831332628147914</v>
       </c>
       <c r="E8">
-        <v>-15.32995422830545</v>
+        <v>-16.57460105776404</v>
       </c>
       <c r="F8">
-        <v>-3.433998872287664</v>
+        <v>-3.186732030919414</v>
       </c>
       <c r="G8">
-        <v>-7.398670791041478</v>
+        <v>-6.332468807476723</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.167732590056387</v>
       </c>
       <c r="E9">
-        <v>-16.18922042572188</v>
+        <v>-16.91807163432736</v>
       </c>
       <c r="F9">
-        <v>-2.388728435269524</v>
+        <v>-3.215747255937273</v>
       </c>
       <c r="G9">
-        <v>-7.363660706074649</v>
+        <v>-6.118899456945292</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.415004546538989</v>
       </c>
       <c r="E10">
-        <v>-15.28398648536225</v>
+        <v>-18.21858330931622</v>
       </c>
       <c r="F10">
-        <v>-2.057583595796005</v>
+        <v>-3.137328199016452</v>
       </c>
       <c r="G10">
-        <v>-6.219410512958563</v>
+        <v>-5.928753706885329</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.577983232518968</v>
       </c>
       <c r="E11">
-        <v>-16.90065306603103</v>
+        <v>-18.32276661539955</v>
       </c>
       <c r="F11">
-        <v>-2.520364299248394</v>
+        <v>-2.881397462982322</v>
       </c>
       <c r="G11">
-        <v>-6.456544444169382</v>
+        <v>-5.479974543906729</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.665687999883503</v>
       </c>
       <c r="E12">
-        <v>-16.80992201142883</v>
+        <v>-19.54763169931798</v>
       </c>
       <c r="F12">
-        <v>-2.349268325669767</v>
+        <v>-2.684971670960892</v>
       </c>
       <c r="G12">
-        <v>-6.049176911895021</v>
+        <v>-4.92811013074802</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.678640525462101</v>
       </c>
       <c r="E13">
-        <v>-18.6764623982446</v>
+        <v>-20.50173232412554</v>
       </c>
       <c r="F13">
-        <v>-1.454228944088541</v>
+        <v>-2.84108082148807</v>
       </c>
       <c r="G13">
-        <v>-6.217136554419703</v>
+        <v>-4.820223721264854</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.62690308781382</v>
       </c>
       <c r="E14">
-        <v>-18.33459911446398</v>
+        <v>-21.57163278709197</v>
       </c>
       <c r="F14">
-        <v>-1.49408915514385</v>
+        <v>-2.506581922400616</v>
       </c>
       <c r="G14">
-        <v>-5.671485713387844</v>
+        <v>-4.273870589937986</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.513230752987709</v>
       </c>
       <c r="E15">
-        <v>-19.31202832728311</v>
+        <v>-21.40776783427086</v>
       </c>
       <c r="F15">
-        <v>-1.376422879045792</v>
+        <v>-2.179866363429865</v>
       </c>
       <c r="G15">
-        <v>-6.03140035197413</v>
+        <v>-4.293633926492713</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.33209769244142</v>
       </c>
       <c r="E16">
-        <v>-20.91905115125564</v>
+        <v>-22.74572486256438</v>
       </c>
       <c r="F16">
-        <v>-1.338571458942271</v>
+        <v>-1.80224597082228</v>
       </c>
       <c r="G16">
-        <v>-4.914281016648893</v>
+        <v>-3.904870560174626</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.085304417863792</v>
       </c>
       <c r="E17">
-        <v>-22.61397253970684</v>
+        <v>-24.14499574964634</v>
       </c>
       <c r="F17">
-        <v>-0.4904334113401494</v>
+        <v>-1.561993744620937</v>
       </c>
       <c r="G17">
-        <v>-4.305207357265119</v>
+        <v>-3.451924648828608</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.766459950905853</v>
       </c>
       <c r="E18">
-        <v>-22.9480651650987</v>
+        <v>-24.55639625063855</v>
       </c>
       <c r="F18">
-        <v>-0.7473921513211533</v>
+        <v>-1.324753462296172</v>
       </c>
       <c r="G18">
-        <v>-4.497300722790053</v>
+        <v>-3.013570189002323</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.370149040889681</v>
       </c>
       <c r="E19">
-        <v>-23.26266676974314</v>
+        <v>-26.33670351071691</v>
       </c>
       <c r="F19">
-        <v>-0.4390315572616345</v>
+        <v>-1.003082660808471</v>
       </c>
       <c r="G19">
-        <v>-4.240426951725826</v>
+        <v>-2.908135268690213</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.900972855346955</v>
       </c>
       <c r="E20">
-        <v>-23.76973234039145</v>
+        <v>-25.84090975560417</v>
       </c>
       <c r="F20">
-        <v>-0.0213587723612902</v>
+        <v>-0.6352825637610738</v>
       </c>
       <c r="G20">
-        <v>-4.070446592887621</v>
+        <v>-2.541571063630361</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.360109286877661</v>
       </c>
       <c r="E21">
-        <v>-25.52164824785328</v>
+        <v>-27.17397014774572</v>
       </c>
       <c r="F21">
-        <v>0.6840043547965168</v>
+        <v>-0.4722499184812975</v>
       </c>
       <c r="G21">
-        <v>-4.100950532690189</v>
+        <v>-2.285026246384614</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.757692887082889</v>
       </c>
       <c r="E22">
-        <v>-25.50785958625485</v>
+        <v>-28.04979104550291</v>
       </c>
       <c r="F22">
-        <v>0.1675437869079147</v>
+        <v>-0.2557660381684803</v>
       </c>
       <c r="G22">
-        <v>-4.237100863116747</v>
+        <v>-2.657686540064716</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.111528305230272</v>
       </c>
       <c r="E23">
-        <v>-26.69889261072123</v>
+        <v>-27.70448890274534</v>
       </c>
       <c r="F23">
-        <v>1.086729249913344</v>
+        <v>0.03018224744089503</v>
       </c>
       <c r="G23">
-        <v>-3.712847684753652</v>
+        <v>-2.323696595268184</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.436077104255113</v>
       </c>
       <c r="E24">
-        <v>-26.25091477759125</v>
+        <v>-28.71447098592847</v>
       </c>
       <c r="F24">
-        <v>0.8376921874053119</v>
+        <v>-0.1516593080868468</v>
       </c>
       <c r="G24">
-        <v>-3.473625157869942</v>
+        <v>-2.719266172735305</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.754155444941474</v>
       </c>
       <c r="E25">
-        <v>-26.90886236245926</v>
+        <v>-28.44495456682071</v>
       </c>
       <c r="F25">
-        <v>0.7213512991517326</v>
+        <v>-0.2947142167133074</v>
       </c>
       <c r="G25">
-        <v>-3.959771908181147</v>
+        <v>-2.392051110152712</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.090054452827423</v>
       </c>
       <c r="E26">
-        <v>-26.48924265625521</v>
+        <v>-28.98847910308403</v>
       </c>
       <c r="F26">
-        <v>1.133199004475591</v>
+        <v>-0.5420862607417126</v>
       </c>
       <c r="G26">
-        <v>-3.788721144060587</v>
+        <v>-2.230720148144867</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.461704577812977</v>
       </c>
       <c r="E27">
-        <v>-25.9941051085318</v>
+        <v>-29.71331623294407</v>
       </c>
       <c r="F27">
-        <v>0.2339979050626994</v>
+        <v>-0.2389029629496908</v>
       </c>
       <c r="G27">
-        <v>-3.21026890798598</v>
+        <v>-2.216491590123299</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.8922633833384641</v>
       </c>
       <c r="E28">
-        <v>-27.34329242024765</v>
+        <v>-28.39381399917243</v>
       </c>
       <c r="F28">
-        <v>0.4918736477586023</v>
+        <v>-0.536655484048959</v>
       </c>
       <c r="G28">
-        <v>-3.021436362455348</v>
+        <v>-2.490293429116305</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.4002857594804501</v>
       </c>
       <c r="E29">
-        <v>-27.37945443125293</v>
+        <v>-28.85046166094299</v>
       </c>
       <c r="F29">
-        <v>0.448232767876916</v>
+        <v>-0.5301710240198445</v>
       </c>
       <c r="G29">
-        <v>-3.243456693228212</v>
+        <v>-2.082406358668312</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.004382030701591673</v>
       </c>
       <c r="E30">
-        <v>-26.18611637450127</v>
+        <v>-29.22607601655482</v>
       </c>
       <c r="F30">
-        <v>0.1645086487440573</v>
+        <v>-0.812037115068224</v>
       </c>
       <c r="G30">
-        <v>-3.103019520183047</v>
+        <v>-2.164200986707892</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.3094950221387282</v>
       </c>
       <c r="E31">
-        <v>-25.0996653644054</v>
+        <v>-28.3441789706294</v>
       </c>
       <c r="F31">
-        <v>0.3537301294633399</v>
+        <v>-0.7172445480636681</v>
       </c>
       <c r="G31">
-        <v>-3.254223403921964</v>
+        <v>-2.171994059312365</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.5109226445970014</v>
       </c>
       <c r="E32">
-        <v>-25.77373571563639</v>
+        <v>-27.86305851112729</v>
       </c>
       <c r="F32">
-        <v>0.4342532395872715</v>
+        <v>-1.184939126949463</v>
       </c>
       <c r="G32">
-        <v>-3.852125687200364</v>
+        <v>-2.456857623137917</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.6137416326016311</v>
       </c>
       <c r="E33">
-        <v>-24.37063972092427</v>
+        <v>-27.90595703090145</v>
       </c>
       <c r="F33">
-        <v>0.8283034712619823</v>
+        <v>-1.061050154921575</v>
       </c>
       <c r="G33">
-        <v>-2.852145240189198</v>
+        <v>-1.817081607362651</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.6220815524373533</v>
       </c>
       <c r="E34">
-        <v>-24.93331263800072</v>
+        <v>-27.87868704534262</v>
       </c>
       <c r="F34">
-        <v>0.1734334791418191</v>
+        <v>-0.9544616361011541</v>
       </c>
       <c r="G34">
-        <v>-2.900618935012398</v>
+        <v>-1.902144887630304</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.5476497839629189</v>
       </c>
       <c r="E35">
-        <v>-24.9477948858904</v>
+        <v>-28.24538445624005</v>
       </c>
       <c r="F35">
-        <v>0.2756034862357074</v>
+        <v>-0.9194067843494846</v>
       </c>
       <c r="G35">
-        <v>-2.619232882982208</v>
+        <v>-2.184191458042046</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.4081883387970066</v>
       </c>
       <c r="E36">
-        <v>-24.91629277799157</v>
+        <v>-27.28222360092737</v>
       </c>
       <c r="F36">
-        <v>0.217873733567207</v>
+        <v>-0.749789446584855</v>
       </c>
       <c r="G36">
-        <v>-3.613720323373672</v>
+        <v>-2.112552626461897</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.2186278340647339</v>
       </c>
       <c r="E37">
-        <v>-24.29498482343119</v>
+        <v>-26.33276626638097</v>
       </c>
       <c r="F37">
-        <v>0.01803589621364588</v>
+        <v>-1.161791228245634</v>
       </c>
       <c r="G37">
-        <v>-3.15569912454253</v>
+        <v>-2.33426227862842</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.003791621727229192</v>
       </c>
       <c r="E38">
-        <v>-24.15418680630818</v>
+        <v>-25.85986501209069</v>
       </c>
       <c r="F38">
-        <v>0.426314166398841</v>
+        <v>-0.546117096523735</v>
       </c>
       <c r="G38">
-        <v>-2.94379542906023</v>
+        <v>-1.919595104477305</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.2410222970700262</v>
       </c>
       <c r="E39">
-        <v>-23.44845652514802</v>
+        <v>-25.80630935205703</v>
       </c>
       <c r="F39">
-        <v>0.6539553272599647</v>
+        <v>-0.4518339754719009</v>
       </c>
       <c r="G39">
-        <v>-3.146180349763331</v>
+        <v>-1.962703719165768</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.4800177434936504</v>
       </c>
       <c r="E40">
-        <v>-21.23252723563105</v>
+        <v>-25.77335777340584</v>
       </c>
       <c r="F40">
-        <v>0.7569479031848328</v>
+        <v>-0.2274068801336392</v>
       </c>
       <c r="G40">
-        <v>-3.331078503195156</v>
+        <v>-1.974303257384084</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.7100801286684855</v>
       </c>
       <c r="E41">
-        <v>-22.32988457866592</v>
+        <v>-24.99373355635432</v>
       </c>
       <c r="F41">
-        <v>0.6989563864170479</v>
+        <v>0.02526257343566877</v>
       </c>
       <c r="G41">
-        <v>-2.620812383459832</v>
+        <v>-2.006313596815724</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.9219937787693794</v>
       </c>
       <c r="E42">
-        <v>-22.19384198850983</v>
+        <v>-24.5490949051295</v>
       </c>
       <c r="F42">
-        <v>1.093500325063827</v>
+        <v>0.03333418540854716</v>
       </c>
       <c r="G42">
-        <v>-3.261214977936965</v>
+        <v>-1.844410881742425</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.112393156106228</v>
       </c>
       <c r="E43">
-        <v>-22.85284448905436</v>
+        <v>-24.60756381416044</v>
       </c>
       <c r="F43">
-        <v>0.3739017040889107</v>
+        <v>-0.1083679992491419</v>
       </c>
       <c r="G43">
-        <v>-3.514760049647523</v>
+        <v>-2.158157112979464</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.281435549377431</v>
       </c>
       <c r="E44">
-        <v>-21.0046903687736</v>
+        <v>-24.09138194465412</v>
       </c>
       <c r="F44">
-        <v>1.208769305898184</v>
+        <v>0.1584590816014125</v>
       </c>
       <c r="G44">
-        <v>-3.031693977953831</v>
+        <v>-2.253869620434268</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.429500323638504</v>
       </c>
       <c r="E45">
-        <v>-20.57880346668038</v>
+        <v>-22.8929811232975</v>
       </c>
       <c r="F45">
-        <v>0.7441761345684701</v>
+        <v>0.2008714926247472</v>
       </c>
       <c r="G45">
-        <v>-3.007698624416909</v>
+        <v>-1.927996480571508</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.562121335962611</v>
       </c>
       <c r="E46">
-        <v>-20.29763521320082</v>
+        <v>-22.46806607265429</v>
       </c>
       <c r="F46">
-        <v>0.9220282726843295</v>
+        <v>0.3060435031863808</v>
       </c>
       <c r="G46">
-        <v>-2.754957662040415</v>
+        <v>-2.317104465175623</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.684746616283328</v>
       </c>
       <c r="E47">
-        <v>-19.41179676972814</v>
+        <v>-22.11267993280004</v>
       </c>
       <c r="F47">
-        <v>0.6912575397754293</v>
+        <v>0.5129754789775169</v>
       </c>
       <c r="G47">
-        <v>-3.316103272220531</v>
+        <v>-2.361267820678895</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.800131915896706</v>
       </c>
       <c r="E48">
-        <v>-18.61390672927003</v>
+        <v>-21.92250853944746</v>
       </c>
       <c r="F48">
-        <v>0.2696715472642601</v>
+        <v>0.3053799808967384</v>
       </c>
       <c r="G48">
-        <v>-2.723325880574486</v>
+        <v>-2.201631231910683</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.914536255079579</v>
       </c>
       <c r="E49">
-        <v>-17.29006231305828</v>
+        <v>-21.40345264770437</v>
       </c>
       <c r="F49">
-        <v>0.6008694022515584</v>
+        <v>0.4477647402943342</v>
       </c>
       <c r="G49">
-        <v>-2.85585510825317</v>
+        <v>-1.91430573593571</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.031191521102894</v>
       </c>
       <c r="E50">
-        <v>-17.15872531133323</v>
+        <v>-20.51584078299598</v>
       </c>
       <c r="F50">
-        <v>0.3479597221354386</v>
+        <v>0.4459746383368845</v>
       </c>
       <c r="G50">
-        <v>-2.626738773681659</v>
+        <v>-2.099817414346447</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.150404504749395</v>
       </c>
       <c r="E51">
-        <v>-16.58851846891354</v>
+        <v>-20.58302312938641</v>
       </c>
       <c r="F51">
-        <v>0.6945817781628637</v>
+        <v>0.5019880137467843</v>
       </c>
       <c r="G51">
-        <v>-3.269579803606892</v>
+        <v>-1.642657761230373</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.274769076881808</v>
       </c>
       <c r="E52">
-        <v>-17.12358083710253</v>
+        <v>-19.72585430368902</v>
       </c>
       <c r="F52">
-        <v>0.7450426068717984</v>
+        <v>0.6881254826254444</v>
       </c>
       <c r="G52">
-        <v>-3.455224629991775</v>
+        <v>-2.203636283756658</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.402066835430396</v>
       </c>
       <c r="E53">
-        <v>-16.91718700031517</v>
+        <v>-19.40322038834237</v>
       </c>
       <c r="F53">
-        <v>0.5020087229318543</v>
+        <v>0.4153416117813588</v>
       </c>
       <c r="G53">
-        <v>-3.806803161098637</v>
+        <v>-2.067893229486313</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.52853718922022</v>
       </c>
       <c r="E54">
-        <v>-16.80755468097367</v>
+        <v>-19.53221913209154</v>
       </c>
       <c r="F54">
-        <v>0.425409589194984</v>
+        <v>0.5026846707325386</v>
       </c>
       <c r="G54">
-        <v>-3.732240295576442</v>
+        <v>-1.881303313559447</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.651261337945727</v>
       </c>
       <c r="E55">
-        <v>-14.86497314801162</v>
+        <v>-19.20687316974977</v>
       </c>
       <c r="F55">
-        <v>0.4348214996255919</v>
+        <v>0.4389492543937419</v>
       </c>
       <c r="G55">
-        <v>-3.700650286023971</v>
+        <v>-2.280245973038286</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.76249274279483</v>
       </c>
       <c r="E56">
-        <v>-15.34268382101605</v>
+        <v>-18.17753296858162</v>
       </c>
       <c r="F56">
-        <v>0.7606672728234026</v>
+        <v>0.5705652375549441</v>
       </c>
       <c r="G56">
-        <v>-3.825537864284466</v>
+        <v>-1.9960089879146</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.856293644311074</v>
       </c>
       <c r="E57">
-        <v>-14.75478845156392</v>
+        <v>-18.12845447035612</v>
       </c>
       <c r="F57">
-        <v>0.6547472464970411</v>
+        <v>0.7438779223034623</v>
       </c>
       <c r="G57">
-        <v>-2.923444674972501</v>
+        <v>-2.22059829136512</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.928698832918455</v>
       </c>
       <c r="E58">
-        <v>-15.40553436799468</v>
+        <v>-17.94504450504036</v>
       </c>
       <c r="F58">
-        <v>0.5150256882994456</v>
+        <v>0.7062253103766135</v>
       </c>
       <c r="G58">
-        <v>-3.318450331607941</v>
+        <v>-2.021236612898528</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.973738338325985</v>
       </c>
       <c r="E59">
-        <v>-13.78240954371579</v>
+        <v>-17.63832154227913</v>
       </c>
       <c r="F59">
-        <v>0.4984807061633311</v>
+        <v>0.644542588461954</v>
       </c>
       <c r="G59">
-        <v>-4.01219304882611</v>
+        <v>-2.406446755828111</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.989885054114381</v>
       </c>
       <c r="E60">
-        <v>-13.39910136412471</v>
+        <v>-17.5505309612949</v>
       </c>
       <c r="F60">
-        <v>0.6429338989657173</v>
+        <v>0.6962426548054768</v>
       </c>
       <c r="G60">
-        <v>-3.335247862307165</v>
+        <v>-2.149622588911115</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.976125644326147</v>
       </c>
       <c r="E61">
-        <v>-14.14023361861772</v>
+        <v>-17.46121199854314</v>
       </c>
       <c r="F61">
-        <v>0.8559527184326242</v>
+        <v>0.7012749867774837</v>
       </c>
       <c r="G61">
-        <v>-4.085421823862247</v>
+        <v>-2.266675322653679</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.929936877404018</v>
       </c>
       <c r="E62">
-        <v>-13.95294455392457</v>
+        <v>-17.18443368943392</v>
       </c>
       <c r="F62">
-        <v>0.8780353366564534</v>
+        <v>0.6996513866679966</v>
       </c>
       <c r="G62">
-        <v>-3.444207287817278</v>
+        <v>-2.370107801864405</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.854637499331764</v>
       </c>
       <c r="E63">
-        <v>-13.40710875555898</v>
+        <v>-16.69057948400988</v>
       </c>
       <c r="F63">
-        <v>0.5214099158728215</v>
+        <v>1.05015517234494</v>
       </c>
       <c r="G63">
-        <v>-3.404589238647133</v>
+        <v>-2.652869716294112</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.752877847284199</v>
       </c>
       <c r="E64">
-        <v>-13.32623742464192</v>
+        <v>-16.38716247746321</v>
       </c>
       <c r="F64">
-        <v>0.6269199003347973</v>
+        <v>0.8388369911559808</v>
       </c>
       <c r="G64">
-        <v>-4.639664625343459</v>
+        <v>-2.762197256791572</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.626240105186079</v>
       </c>
       <c r="E65">
-        <v>-14.22828585191541</v>
+        <v>-16.68326152565553</v>
       </c>
       <c r="F65">
-        <v>0.6650902418883957</v>
+        <v>0.7402828077753124</v>
       </c>
       <c r="G65">
-        <v>-4.553361241395028</v>
+        <v>-2.525682072048846</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.48079699430169</v>
       </c>
       <c r="E66">
-        <v>-12.66792851038865</v>
+        <v>-16.12102054255687</v>
       </c>
       <c r="F66">
-        <v>0.2266643684457154</v>
+        <v>0.6103277012567232</v>
       </c>
       <c r="G66">
-        <v>-4.732173749184968</v>
+        <v>-2.670275550483064</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.319162528431807</v>
       </c>
       <c r="E67">
-        <v>-12.7290264021882</v>
+        <v>-15.89681358239732</v>
       </c>
       <c r="F67">
-        <v>0.3425976999371174</v>
+        <v>0.6174268098987149</v>
       </c>
       <c r="G67">
-        <v>-4.164676197414673</v>
+        <v>-2.383550525764047</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.143272449449766</v>
       </c>
       <c r="E68">
-        <v>-13.09680572463574</v>
+        <v>-16.47195028665958</v>
       </c>
       <c r="F68">
-        <v>0.6886498391914164</v>
+        <v>0.6349509223049385</v>
       </c>
       <c r="G68">
-        <v>-4.136681183164165</v>
+        <v>-2.666764099008017</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.957000874823314</v>
       </c>
       <c r="E69">
-        <v>-13.04490719592068</v>
+        <v>-15.81031880334644</v>
       </c>
       <c r="F69">
-        <v>0.8235304182870515</v>
+        <v>1.040734978240304</v>
       </c>
       <c r="G69">
-        <v>-4.246854604909146</v>
+        <v>-2.55594321260444</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.759689674555935</v>
       </c>
       <c r="E70">
-        <v>-12.11314669482938</v>
+        <v>-15.64682763954457</v>
       </c>
       <c r="F70">
-        <v>0.7000763391456328</v>
+        <v>0.86227481845079</v>
       </c>
       <c r="G70">
-        <v>-3.811721803908295</v>
+        <v>-1.943000429736636</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.551611537792643</v>
       </c>
       <c r="E71">
-        <v>-12.92257435634786</v>
+        <v>-15.34149600257715</v>
       </c>
       <c r="F71">
-        <v>-0.08950027491557754</v>
+        <v>0.8165704753687301</v>
       </c>
       <c r="G71">
-        <v>-4.38587936513052</v>
+        <v>-2.448850469476973</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.333221916221877</v>
       </c>
       <c r="E72">
-        <v>-12.24594562694077</v>
+        <v>-15.50302685063371</v>
       </c>
       <c r="F72">
-        <v>0.2973340483133468</v>
+        <v>0.6330291099304436</v>
       </c>
       <c r="G72">
-        <v>-2.807389245663743</v>
+        <v>-1.736936969904656</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.102757643512027</v>
       </c>
       <c r="E73">
-        <v>-13.01653660936078</v>
+        <v>-15.68580137461676</v>
       </c>
       <c r="F73">
-        <v>0.2696955699189413</v>
+        <v>0.726352981529836</v>
       </c>
       <c r="G73">
-        <v>-3.099628162959191</v>
+        <v>-2.111529214582181</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.8619003174722689</v>
       </c>
       <c r="E74">
-        <v>-13.86103398730612</v>
+        <v>-15.16322355967021</v>
       </c>
       <c r="F74">
-        <v>0.08311161101017224</v>
+        <v>0.1874304031469224</v>
       </c>
       <c r="G74">
-        <v>-3.636191002069384</v>
+        <v>-1.741915659839908</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.6114906943583995</v>
       </c>
       <c r="E75">
-        <v>-12.13180707331183</v>
+        <v>-15.10673157922989</v>
       </c>
       <c r="F75">
-        <v>0.3824960158929556</v>
+        <v>0.2890694267356161</v>
       </c>
       <c r="G75">
-        <v>-3.109990208241319</v>
+        <v>-1.605256234218084</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.3512703140000318</v>
       </c>
       <c r="E76">
-        <v>-14.0981283622066</v>
+        <v>-15.14984191278161</v>
       </c>
       <c r="F76">
-        <v>-0.165131875525978</v>
+        <v>0.3992323508991168</v>
       </c>
       <c r="G76">
-        <v>-3.390775789015553</v>
+        <v>-1.451773170451125</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.084450513484349</v>
       </c>
       <c r="E77">
-        <v>-12.78383217883064</v>
+        <v>-15.46175638969888</v>
       </c>
       <c r="F77">
-        <v>0.01363975040698891</v>
+        <v>0.2268167880478305</v>
       </c>
       <c r="G77">
-        <v>-2.849555381554813</v>
+        <v>-0.6606000758371989</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.1870880019332745</v>
       </c>
       <c r="E78">
-        <v>-13.31436754667556</v>
+        <v>-15.34083979518783</v>
       </c>
       <c r="F78">
-        <v>-0.8510416225964414</v>
+        <v>0.3862750279845269</v>
       </c>
       <c r="G78">
-        <v>-2.863843986701976</v>
+        <v>-0.3569052112759459</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.4608208824322486</v>
       </c>
       <c r="E79">
-        <v>-13.33683226673156</v>
+        <v>-15.55737162081909</v>
       </c>
       <c r="F79">
-        <v>-0.5682320210762735</v>
+        <v>-0.2490322395511231</v>
       </c>
       <c r="G79">
-        <v>-2.361933560549629</v>
+        <v>-0.7150079931159997</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.7307666344409249</v>
       </c>
       <c r="E80">
-        <v>-13.11454824341541</v>
+        <v>-16.22637920744512</v>
       </c>
       <c r="F80">
-        <v>-0.2582909020122132</v>
+        <v>-0.09981013561082018</v>
       </c>
       <c r="G80">
-        <v>-1.904922719875249</v>
+        <v>-0.7699511130359789</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.9929918259290099</v>
       </c>
       <c r="E81">
-        <v>-14.09056951759542</v>
+        <v>-16.10228955948189</v>
       </c>
       <c r="F81">
-        <v>-0.6393746987309034</v>
+        <v>-0.3455660348363635</v>
       </c>
       <c r="G81">
-        <v>-2.330100751750185</v>
+        <v>0.06101495063569552</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.242348810607574</v>
       </c>
       <c r="E82">
-        <v>-15.18402284198495</v>
+        <v>-16.89461014355341</v>
       </c>
       <c r="F82">
-        <v>-0.8313455308600776</v>
+        <v>-0.5356813239832668</v>
       </c>
       <c r="G82">
-        <v>-3.034383044882679</v>
+        <v>0.249377562139928</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.471591716704789</v>
       </c>
       <c r="E83">
-        <v>-15.60638366766339</v>
+        <v>-17.47148289014944</v>
       </c>
       <c r="F83">
-        <v>-0.8143018715474778</v>
+        <v>-0.8046199133435571</v>
       </c>
       <c r="G83">
-        <v>-1.263624640003363</v>
+        <v>-0.02841088384370785</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.675252110217186</v>
       </c>
       <c r="E84">
-        <v>-16.43013575504121</v>
+        <v>-17.74383802919772</v>
       </c>
       <c r="F84">
-        <v>-0.6679989343346403</v>
+        <v>-0.8881996991838188</v>
       </c>
       <c r="G84">
-        <v>-1.744249665504364</v>
+        <v>0.2619900692595963</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.846661215606123</v>
       </c>
       <c r="E85">
-        <v>-17.22837051203928</v>
+        <v>-19.13586156251786</v>
       </c>
       <c r="F85">
-        <v>-1.259059785417157</v>
+        <v>-0.9401052006432359</v>
       </c>
       <c r="G85">
-        <v>-1.203240728355504</v>
+        <v>0.1573592582815491</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.979211541633668</v>
       </c>
       <c r="E86">
-        <v>-18.39997066071679</v>
+        <v>-19.09826254039418</v>
       </c>
       <c r="F86">
-        <v>-1.348484531651573</v>
+        <v>-1.218262690829282</v>
       </c>
       <c r="G86">
-        <v>-1.765822248060733</v>
+        <v>0.5206809185592384</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.067886568852765</v>
       </c>
       <c r="E87">
-        <v>-20.14110898479068</v>
+        <v>-20.20081555079642</v>
       </c>
       <c r="F87">
-        <v>-1.243358909664496</v>
+        <v>-1.638688968976532</v>
       </c>
       <c r="G87">
-        <v>-1.082715704306759</v>
+        <v>0.4047455835016707</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.10791422997431</v>
       </c>
       <c r="E88">
-        <v>-19.48650888825048</v>
+        <v>-21.34709772323777</v>
       </c>
       <c r="F88">
-        <v>-1.299880074292312</v>
+        <v>-1.628223375209563</v>
       </c>
       <c r="G88">
-        <v>-1.573423425418639</v>
+        <v>0.6492392037148388</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.095488366588217</v>
       </c>
       <c r="E89">
-        <v>-22.25650148776753</v>
+        <v>-23.24662291439532</v>
       </c>
       <c r="F89">
-        <v>-1.67766696874786</v>
+        <v>-1.743295204602053</v>
       </c>
       <c r="G89">
-        <v>-0.7819631488996911</v>
+        <v>0.7756331816044063</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.027424448929216</v>
       </c>
       <c r="E90">
-        <v>-24.0787146501134</v>
+        <v>-23.97397066050122</v>
       </c>
       <c r="F90">
-        <v>-1.60001166657242</v>
+        <v>-2.417502605373168</v>
       </c>
       <c r="G90">
-        <v>-0.9630208970379885</v>
+        <v>0.7423122483880275</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.902144129456123</v>
       </c>
       <c r="E91">
-        <v>-24.82545373989492</v>
+        <v>-25.52318493604346</v>
       </c>
       <c r="F91">
-        <v>-1.300628918424442</v>
+        <v>-2.821654777525019</v>
       </c>
       <c r="G91">
-        <v>-1.192930897965198</v>
+        <v>0.9703738421447285</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.720664876032051</v>
       </c>
       <c r="E92">
-        <v>-26.69471863333978</v>
+        <v>-27.2361603341237</v>
       </c>
       <c r="F92">
-        <v>-2.304365013866215</v>
+        <v>-2.86392719445728</v>
       </c>
       <c r="G92">
-        <v>-0.4587320825631374</v>
+        <v>0.320243613321107</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.486056110111394</v>
       </c>
       <c r="E93">
-        <v>-28.77432291433057</v>
+        <v>-28.87697991525202</v>
       </c>
       <c r="F93">
-        <v>-2.46093805013896</v>
+        <v>-3.387057776673224</v>
       </c>
       <c r="G93">
-        <v>-1.88785367173855</v>
+        <v>0.8885661603821937</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.205904021855646</v>
       </c>
       <c r="E94">
-        <v>-30.89610097971934</v>
+        <v>-30.73536131842016</v>
       </c>
       <c r="F94">
-        <v>-2.09081438252671</v>
+        <v>-3.71602069640777</v>
       </c>
       <c r="G94">
-        <v>-1.918884981948523</v>
+        <v>0.06367791011863108</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.891412020371496</v>
       </c>
       <c r="E95">
-        <v>-32.35057635173092</v>
+        <v>-33.22676065547903</v>
       </c>
       <c r="F95">
-        <v>-2.749986086569611</v>
+        <v>-4.292388794866832</v>
       </c>
       <c r="G95">
-        <v>-2.247909290532756</v>
+        <v>0.2444641408194528</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.5554717401757026</v>
       </c>
       <c r="E96">
-        <v>-35.99178601425159</v>
+        <v>-34.63105069844705</v>
       </c>
       <c r="F96">
-        <v>-3.007953778047225</v>
+        <v>-4.348359923539189</v>
       </c>
       <c r="G96">
-        <v>-2.391445417407574</v>
+        <v>-0.4718432418997083</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.2153783410931732</v>
       </c>
       <c r="E97">
-        <v>-37.18112037528611</v>
+        <v>-37.64001700098907</v>
       </c>
       <c r="F97">
-        <v>-3.207646651105296</v>
+        <v>-4.919785982073149</v>
       </c>
       <c r="G97">
-        <v>-2.461324607133312</v>
+        <v>-0.370319216985086</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.1105152622007971</v>
       </c>
       <c r="E98">
-        <v>-40.52619568731819</v>
+        <v>-39.20119252514682</v>
       </c>
       <c r="F98">
-        <v>-3.581681869593565</v>
+        <v>-5.518291371004626</v>
       </c>
       <c r="G98">
-        <v>-2.736288227469363</v>
+        <v>-1.219523942370278</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.4030999784379099</v>
       </c>
       <c r="E99">
-        <v>-41.34027079230916</v>
+        <v>-42.12533986940753</v>
       </c>
       <c r="F99">
-        <v>-3.972843584134715</v>
+        <v>-5.581190964633998</v>
       </c>
       <c r="G99">
-        <v>-3.465401312407935</v>
+        <v>-1.190393254222636</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.6442912197287824</v>
       </c>
       <c r="E100">
-        <v>-44.45475358176977</v>
+        <v>-43.53263891398038</v>
       </c>
       <c r="F100">
-        <v>-4.061327304999549</v>
+        <v>-6.106842268856661</v>
       </c>
       <c r="G100">
-        <v>-3.334947626679186</v>
+        <v>-1.824274208711168</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.815580912613127</v>
       </c>
       <c r="E101">
-        <v>-46.40922991196613</v>
+        <v>-46.65817028386786</v>
       </c>
       <c r="F101">
-        <v>-3.857524072888787</v>
+        <v>-6.332883852262978</v>
       </c>
       <c r="G101">
-        <v>-3.114431084790803</v>
+        <v>-2.33499067636934</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.9086740535779934</v>
       </c>
       <c r="E102">
-        <v>-48.30175278883003</v>
+        <v>-48.6820031665832</v>
       </c>
       <c r="F102">
-        <v>-4.873201912809317</v>
+        <v>-6.718169128448668</v>
       </c>
       <c r="G102">
-        <v>-3.746774310715169</v>
+        <v>-2.451150535461744</v>
       </c>
     </row>
   </sheetData>
